--- a/tmp/报价 - 数据测试-施耐德.xlsx
+++ b/tmp/报价 - 数据测试-施耐德.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\joii\project\cpq\tmp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1AD55B8-5FA2-4775-9437-C418E06C80A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F962180B-1E3C-4F1B-8B5D-1F2EE06A64EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="912" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="405" yWindow="1170" windowWidth="28395" windowHeight="14640" tabRatio="912" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="物料" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="142">
   <si>
     <t>销售料号</t>
   </si>
@@ -512,6 +512,14 @@
   </si>
   <si>
     <t>000000</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>结算单位</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>g</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -1256,7 +1264,7 @@
     <col min="5" max="5" width="11.625" customWidth="1"/>
     <col min="6" max="6" width="10.375" customWidth="1"/>
     <col min="7" max="7" width="12.125" style="35" customWidth="1"/>
-    <col min="8" max="8" width="11.375" style="35" customWidth="1"/>
+    <col min="8" max="8" width="14" style="35" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1998,6 +2006,9 @@
       <c r="E1" s="9" t="s">
         <v>0</v>
       </c>
+      <c r="F1" s="51" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="2" spans="1:6" ht="16.5" customHeight="1" thickBot="1">
       <c r="A2" s="43" t="s">
@@ -2011,7 +2022,9 @@
       <c r="E2" s="45" t="s">
         <v>134</v>
       </c>
-      <c r="F2" s="45"/>
+      <c r="F2" s="45" t="s">
+        <v>141</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
@@ -2903,7 +2916,7 @@
     <col min="1" max="1" width="13.125" style="35" customWidth="1"/>
     <col min="2" max="2" width="5.375" style="35" customWidth="1"/>
     <col min="3" max="3" width="37.625" style="35" customWidth="1"/>
-    <col min="4" max="4" width="13.125" style="35" customWidth="1"/>
+    <col min="4" max="4" width="18.875" style="35" customWidth="1"/>
     <col min="5" max="5" width="9.75" style="35" customWidth="1"/>
     <col min="6" max="6" width="11.125" style="35" customWidth="1"/>
     <col min="7" max="7" width="16" style="35" customWidth="1"/>
